--- a/data/trans_camb/P57_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Estudios-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 4,19</t>
+          <t>-5,84; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 1,95</t>
+          <t>-7,21; 1,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,34</t>
+          <t>-5,12; 1,22</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 15,16</t>
+          <t>-18,1; 13,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 5,06</t>
+          <t>-17,56; 3,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 3,8</t>
+          <t>-13,78; 3,74</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -4,1</t>
+          <t>-9,86; -3,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,14; -6,01</t>
+          <t>-12,05; -6,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -5,41</t>
+          <t>-9,81; -5,57</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,69; -27,05</t>
+          <t>-57,53; -26,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,14; -32,37</t>
+          <t>-59,51; -33,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,32; -32,41</t>
+          <t>-53,65; -33,0</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 1,06</t>
+          <t>-6,28; 0,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 2,47</t>
+          <t>-4,04; 2,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,73</t>
+          <t>-3,92; 0,6</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 11,65</t>
+          <t>-46,29; 8,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 37,83</t>
+          <t>-37,0; 31,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 7,75</t>
+          <t>-33,04; 8,6</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -4,2</t>
+          <t>-8,83; -3,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,72; -5,68</t>
+          <t>-10,92; -5,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -5,35</t>
+          <t>-8,91; -5,36</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,47; -23,32</t>
+          <t>-47,34; -22,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,81; -25,59</t>
+          <t>-44,72; -24,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,19; -26,13</t>
+          <t>-42,52; -26,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,71</t>
+          <t>-2,45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-2,09</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 3,86</t>
+          <t>-7,22; 2,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 1,23</t>
+          <t>-6,6; 1,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 1,22</t>
+          <t>-5,36; 1,11</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-3,54%</t>
+          <t>-6,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-6,95%</t>
+          <t>-6,27%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-5,16%</t>
+          <t>-5,93%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 13,5</t>
+          <t>-21,65; 9,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 3,08</t>
+          <t>-15,82; 4,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 3,74</t>
+          <t>-14,45; 3,3</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-5,17</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-8,56</t>
+          <t>-6,52</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-7,46</t>
+          <t>-5,82</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -3,99</t>
+          <t>-7,32; -2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -6,22</t>
+          <t>-8,7; -4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -5,57</t>
+          <t>-7,34; -4,3</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-39,65%</t>
+          <t>-31,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-43,76%</t>
+          <t>-33,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-41,82%</t>
+          <t>-32,64%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,53; -26,51</t>
+          <t>-42,04; -19,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,51; -33,19</t>
+          <t>-41,57; -23,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,65; -33,0</t>
+          <t>-38,97; -25,1</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,48</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 0,82</t>
+          <t>-5,78; 1,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,27</t>
+          <t>-4,14; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 0,6</t>
+          <t>-3,99; 1,12</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-21,21%</t>
+          <t>-20,08%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-8,8%</t>
+          <t>-7,62%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-15,68%</t>
+          <t>-14,54%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,29; 8,73</t>
+          <t>-44,6; 13,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 31,88</t>
+          <t>-35,5; 33,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 8,6</t>
+          <t>-33,66; 14,04</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-6,07</t>
+          <t>-5,12</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-7,73</t>
+          <t>-6,15</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,91</t>
+          <t>-5,64</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -3,93</t>
+          <t>-6,98; -3,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -5,5</t>
+          <t>-7,88; -4,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,91; -5,36</t>
+          <t>-7,06; -4,47</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-32,77%</t>
+          <t>-27,64%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-33,02%</t>
+          <t>-26,28%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-32,87%</t>
+          <t>-26,82%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,34; -22,65</t>
+          <t>-35,6; -19,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,72; -24,78</t>
+          <t>-32,19; -19,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,52; -26,54</t>
+          <t>-32,1; -22,02</t>
         </is>
       </c>
     </row>
